--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:00</t>
+          <t>2026-09-09 00:51:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:01</t>
+          <t>2026-09-09 00:51:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:38:02</t>
+          <t>2026-09-09 00:51:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">

--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:09</t>
+          <t>2026-09-09 01:16:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:10</t>
+          <t>2026-09-09 01:16:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 00:51:11</t>
+          <t>2026-09-09 01:16:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">

--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.95%3285</t>
+          <t>+2.89%3380</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.95%</t>
+          <t>+2.89%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3285</v>
+        <v>3380</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.99%1,001,000</t>
+          <t>8.13%1,001,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>8.13%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.41%2470</t>
+          <t>-0.2%2465</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2470</v>
+        <v>2465</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.69%1,116,000</t>
+          <t>6.61%1,116,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.69%</t>
+          <t>6.61%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-9.96%12520</t>
+          <t>-0.96%12400</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.96%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>12520</v>
+        <v>12400</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.23%205,000</t>
+          <t>6.11%205,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.11%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.82%5340</t>
+          <t>+0.66%5375</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5340</v>
+        <v>5375</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.03%465,000</t>
+          <t>6.00%465,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.53%954</t>
+          <t>+4.09%993</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.53%</t>
+          <t>+4.09%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>954</v>
+        <v>993</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.75%2,482,000</t>
+          <t>5.92%2,482,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.75%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.52%1935</t>
+          <t>+2.07%1975</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-6.52%</t>
+          <t>+2.07%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1935</v>
+        <v>1975</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.46%1,161,000</t>
+          <t>5.51%1,161,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.9%1955</t>
+          <t>+9.8%1345</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1955</v>
+        <v>1345</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.10%1,074,000</t>
+          <t>5.27%1,630,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>5.27%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1074000</v>
+        <v>1630000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>+0.48%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.21%1225</t>
+          <t>+3.07%2015</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+3.07%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1225</v>
+        <v>2015</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.85%1,630,000</t>
+          <t>5.20%1,074,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.85%</t>
+          <t>5.20%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1630000</v>
+        <v>1074000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.4%6500</t>
+          <t>+5.69%6870</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>+5.69%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6500</v>
+        <v>6870</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.63%293,000</t>
+          <t>4.83%293,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.63%</t>
+          <t>4.83%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+5.56%5795</t>
+          <t>-3.11%5615</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+5.56%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5795</v>
+        <v>5615</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.77%268,000</t>
+          <t>3.61%268,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.61%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,33 +1119,33 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.85%135</t>
+          <t>-6.67%126</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.85%</t>
+          <t>-6.67%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.57%10,877,000</t>
+          <t>3.46%11,420,868</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>10877000</v>
+        <v>11420868</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-5.33%186.5</t>
+          <t>+1.34%189</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-5.33%</t>
+          <t>+1.34%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>186.5</v>
+        <v>189</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.28%7,245,000</t>
+          <t>3.29%7,245,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.28%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.75%602</t>
+          <t>-2.66%586</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>602</v>
+        <v>586</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.26%2,231,000</t>
+          <t>3.14%2,231,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1.95%235</t>
+          <t>+0.64%236.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1.95%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>235</v>
+        <v>236.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.11%5,445,000</t>
+          <t>3.09%5,445,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:39</t>
+          <t>2026-09-09 19:33:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.6%450</t>
+          <t>-1.67%442.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>450</v>
+        <v>442.5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.93%2,682,000</t>
+          <t>2.85%2,682,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.85%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3%515</t>
+          <t>+3.5%533</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+3.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.69%2,150,000</t>
+          <t>2.75%2,150,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.69%</t>
+          <t>2.75%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.02%2340</t>
+          <t>+8.29%1110</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.02%</t>
+          <t>+8.29%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2340</v>
+        <v>1110</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.44%429,675</t>
+          <t>2.58%968,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.58%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>429675</v>
+        <v>968000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.38%1025</t>
+          <t>-0.64%2325</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1025</v>
+        <v>2325</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.41%968,000</t>
+          <t>2.40%429,675</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.40%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>968000</v>
+        <v>429675</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+0.42%5960</t>
+          <t>-0.59%5925</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5960</v>
+        <v>5925</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.37%164,000</t>
+          <t>2.33%164,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.37%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-0.25%4030</t>
+          <t>-3.1%3905</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4030</v>
+        <v>3905</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.10%215,000</t>
+          <t>2.02%215,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.05%4710</t>
+          <t>+1.5%812</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.05%</t>
+          <t>+1.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>4710</v>
+        <v>812</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.66%145,000</t>
+          <t>1.65%844,013</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>145000</v>
+        <v>844013</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,34 +1785,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.6%800</t>
+          <t>-1.8%4625</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>800</v>
+        <v>4625</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.64%844,013</t>
+          <t>1.61%145,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>844013</v>
+        <v>145000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.8%505</t>
+          <t>-0.59%502</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.8%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.23%1,000,000</t>
+          <t>1.21%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+0.03%19220</t>
+          <t>-5.45%7280</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>19220</v>
+        <v>7280</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.51%11,000</t>
+          <t>0.89%51,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>11000</v>
+        <v>51000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3.11%747</t>
+          <t>-3.2%18605</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3.11%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>747</v>
+        <v>18605</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.47%261,000</t>
+          <t>0.49%11,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>261000</v>
+        <v>11000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.68%291</t>
+          <t>+1.47%758</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.68%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>291</v>
+        <v>758</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.47%659,000</t>
+          <t>0.48%261,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>659000</v>
+        <v>261000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.58%510</t>
+          <t>+2.55%523</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.58%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.46%373,000</t>
+          <t>0.47%373,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.1%968</t>
+          <t>+0.52%292.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>968</v>
+        <v>292.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.46%196,000</t>
+          <t>0.46%659,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>196000</v>
+        <v>659000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.09%1385</t>
+          <t>+1.14%979</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.09%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1385</v>
+        <v>979</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.45%134,000</t>
+          <t>0.46%196,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>134000</v>
+        <v>196000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:40</t>
+          <t>2026-09-09 19:33:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6139亞翔</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.41%742</t>
+          <t>+3.78%5760</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+3.78%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>742</v>
+        <v>5760</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.45%250,000</t>
+          <t>0.46%33,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>250000</v>
+        <v>33000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>6139亞翔</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.86%5550</t>
+          <t>+1.08%750</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>5550</v>
+        <v>750</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.44%33,000</t>
+          <t>0.45%250,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>33000</v>
+        <v>250000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-2.06%357</t>
+          <t>-0.52%2850</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-2.06%</t>
+          <t>-0.52%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>357</v>
+        <v>2850</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.44%508,000</t>
+          <t>0.43%63,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>508000</v>
+        <v>63000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>8150南茂</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.68%2865</t>
+          <t>+1.33%91.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.68%</t>
+          <t>+1.33%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2865</v>
+        <v>91.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.44%63,000</t>
+          <t>0.43%1,957,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>63000</v>
+        <v>1957000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,25 +2517,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8150南茂</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.1%90.3</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>90.3</v>
+        <v>1330</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.43%1,957,000</t>
+          <t>0.43%134,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2544,11 +2544,11 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>1957000</v>
+        <v>134000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.57%2265</t>
+          <t>-2.1%349.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.57%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2265</v>
+        <v>349.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.42%76,000</t>
+          <t>0.43%508,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>76000</v>
+        <v>508000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.31%1055</t>
+          <t>+3.09%2335</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.31%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1055</v>
+        <v>2335</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.40%155,000</t>
+          <t>0.43%76,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>155000</v>
+        <v>76000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-1.82%1345</t>
+          <t>+0.95%1065</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1345</v>
+        <v>1065</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.37%113,000</t>
+          <t>0.40%155,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>113000</v>
+        <v>155000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>5289宜鼎</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.49%1370</t>
+          <t>+3.56%640</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.56%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1370</v>
+        <v>640</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.33%99,952</t>
+          <t>0.38%250,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>99952</v>
+        <v>250000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 01:16:42</t>
+          <t>2026-09-09 19:33:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,41 +2822,163 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>6274台燿</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0%1345</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>1345</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.36%113,000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>113000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:33:51</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>5289宜鼎</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-1.09%1355</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>1355</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.33%99,952</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>99952</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-0.00%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-09-09 19:33:51</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>5347世界</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-2.56%152</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-2.56%</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>152</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>0.23%629,000</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0.23%</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>+3.29%157</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>+3.29%</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>157</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.24%629,000</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.24%</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
         <v>629000</v>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>-0.01%</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>+0.01%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:48</t>
+          <t>2026-09-09 22:37:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:49</t>
+          <t>2026-09-09 22:37:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 19:33:51</t>
+          <t>2026-09-09 22:37:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:13</t>
+          <t>2026-09-09 22:49:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:15</t>
+          <t>2026-09-09 22:49:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:37:16</t>
+          <t>2026-09-09 22:49:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">

--- a/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-09_00992A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:07</t>
+          <t>2026-09-09 23:10:12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:08</t>
+          <t>2026-09-09 23:10:13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-09 22:49:09</t>
+          <t>2026-09-09 23:10:14</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
